--- a/output/pdf_financials_xlsx/FURY.xlsx
+++ b/output/pdf_financials_xlsx/FURY.xlsx
@@ -1213,16 +1213,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.07166</v>
+        <v>-0.07166</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.07413</v>
+        <v>-0.07413</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.171505</v>
+        <v>-0.171505</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.888419</v>
+        <v>-0.888419</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>0.6</v>
@@ -1256,10 +1256,10 @@
         </is>
       </c>
       <c r="M16" s="3" t="n">
-        <v>108.138</v>
+        <v>-108.138</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>6.459</v>
+        <v>-6.459</v>
       </c>
     </row>
     <row r="17">
@@ -1469,16 +1469,16 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.07166</v>
+        <v>-0.07166</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.07413</v>
+        <v>-0.07413</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.171505</v>
+        <v>-0.171505</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.888419</v>
+        <v>-0.888419</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0.522</v>
@@ -1512,10 +1512,10 @@
         </is>
       </c>
       <c r="M20" s="3" t="n">
-        <v>108.138</v>
+        <v>-108.138</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>6.459</v>
+        <v>-6.459</v>
       </c>
     </row>
     <row r="21">
@@ -1637,16 +1637,16 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.07166</v>
+        <v>-0.07166</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.07413</v>
+        <v>-0.07413</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.171505</v>
+        <v>-0.171505</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.888419</v>
+        <v>-0.888419</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0.522</v>
@@ -1670,10 +1670,10 @@
         <v>-17.213</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>108.138</v>
+        <v>-108.138</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>6.459</v>
+        <v>-6.459</v>
       </c>
     </row>
     <row r="24">
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>3.583</v>
+        <v>-3.583</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>3.7065</v>
+        <v>-3.7065</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-8.57525</v>
+        <v>8.57525</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-12.6917</v>
+        <v>12.6917</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>148.134247</v>
+        <v>-148.134247</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>161.475</v>
+        <v>-161.475</v>
       </c>
     </row>
     <row r="27">
@@ -1863,16 +1863,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.07166</v>
+        <v>-0.07166</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.07413</v>
+        <v>-0.07413</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.171505</v>
+        <v>-0.171505</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.888419</v>
+        <v>-0.888419</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.6</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>108.138</v>
+        <v>-108.138</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>6.459</v>
+        <v>-6.459</v>
       </c>
     </row>
     <row r="28">
@@ -1975,16 +1975,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.07166</v>
+        <v>-0.07166</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.07413</v>
+        <v>-0.07413</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.171505</v>
+        <v>-0.171505</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.888419</v>
+        <v>-0.888419</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.6</v>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>108.435</v>
+        <v>-107.841</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6.663</v>
+        <v>-6.255</v>
       </c>
     </row>
     <row r="30">
@@ -2103,16 +2103,16 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>13</v>
@@ -2146,10 +2146,10 @@
         </is>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5381,16 +5381,16 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>0.07166</v>
+        <v>-0.07166</v>
       </c>
       <c r="C99" s="3" t="n">
-        <v>0.07413</v>
+        <v>-0.07413</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.171505</v>
+        <v>-0.171505</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.888419</v>
+        <v>-0.888419</v>
       </c>
       <c r="F99" s="3" t="n">
         <v>0.522</v>
@@ -6261,10 +6261,10 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.37163</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.707668</v>
+        <v>0.447263</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -35016,7 +35016,11 @@
           <t>Exploration and evaluation expenditure</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -39451,10 +39455,10 @@
         </is>
       </c>
       <c r="P403" s="5" t="n">
-        <v>108.138</v>
+        <v>-108.138</v>
       </c>
       <c r="Q403" s="5" t="n">
-        <v>6.459</v>
+        <v>-6.459</v>
       </c>
     </row>
     <row r="404">
@@ -39534,10 +39538,10 @@
         </is>
       </c>
       <c r="P404" s="5" t="n">
-        <v>108.141</v>
+        <v>-108.141</v>
       </c>
       <c r="Q404" s="5" t="n">
-        <v>6.478</v>
+        <v>-6.478</v>
       </c>
     </row>
     <row r="405">
@@ -45264,10 +45268,10 @@
         </is>
       </c>
       <c r="G477" s="5" t="n">
-        <v>0.171505</v>
+        <v>-0.171505</v>
       </c>
       <c r="H477" s="5" t="n">
-        <v>0.888419</v>
+        <v>-0.888419</v>
       </c>
       <c r="I477" t="inlineStr">
         <is>
@@ -45507,10 +45511,10 @@
         </is>
       </c>
       <c r="G480" s="5" t="n">
-        <v>0.180542</v>
+        <v>-0.180542</v>
       </c>
       <c r="H480" s="5" t="n">
-        <v>0.897248</v>
+        <v>-0.897248</v>
       </c>
       <c r="I480" t="inlineStr">
         <is>
@@ -45994,10 +45998,10 @@
         </is>
       </c>
       <c r="F486" s="5" t="n">
-        <v>0.07413</v>
+        <v>-0.07413</v>
       </c>
       <c r="G486" s="5" t="n">
-        <v>0.174639</v>
+        <v>-0.174639</v>
       </c>
       <c r="H486" t="inlineStr">
         <is>
@@ -46884,10 +46888,10 @@
         </is>
       </c>
       <c r="E497" s="5" t="n">
-        <v>0.07166</v>
+        <v>-0.07166</v>
       </c>
       <c r="F497" s="5" t="n">
-        <v>0.07413</v>
+        <v>-0.07413</v>
       </c>
       <c r="G497" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FURY.xlsx
+++ b/output/pdf_financials_xlsx/FURY.xlsx
@@ -992,13 +992,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000982</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-4.9e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.014915</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.257</v>
       </c>
     </row>
     <row r="13">
@@ -1866,13 +1866,13 @@
         <v>-0.07166</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.07413</v>
+        <v>-0.073148</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.171505</v>
+        <v>-0.171456</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.888419</v>
+        <v>-0.8735039999999999</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>0.6</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-108.138</v>
+        <v>-107.838</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-6.459</v>
+        <v>-6.202</v>
       </c>
     </row>
     <row r="28">
@@ -1978,13 +1978,13 @@
         <v>-0.07166</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.07413</v>
+        <v>-0.073148</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.171505</v>
+        <v>-0.171456</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.888419</v>
+        <v>-0.8735039999999999</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>0.6</v>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-107.841</v>
+        <v>-107.541</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-6.255</v>
+        <v>-5.998</v>
       </c>
     </row>
     <row r="30">
@@ -2256,25 +2256,25 @@
         <v>3.601317</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.457</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.474</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>3.259</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>10.309</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>7.313</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.912</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>21.197</v>
       </c>
     </row>
     <row r="35">
@@ -2350,25 +2350,25 @@
         <v>3.601317</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.625</v>
+        <v>3.082</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.425</v>
+        <v>2.899</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.605</v>
+        <v>3.864</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.582</v>
+        <v>10.891</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>1.166</v>
+        <v>8.478999999999999</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>2.358</v>
+        <v>7.27</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>7.783</v>
+        <v>28.98</v>
       </c>
     </row>
     <row r="37">
@@ -2924,25 +2924,25 @@
         <v>0.092655</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.936</v>
+        <v>0.479</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>3.421</v>
+        <v>0.947</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.761</v>
+        <v>0.502</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>10.911</v>
+        <v>0.602</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>7.905</v>
+        <v>0.592</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>7.497</v>
+        <v>2.585</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>23.819</v>
+        <v>2.622</v>
       </c>
     </row>
     <row r="49">
@@ -6563,19 +6563,19 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.235</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.214</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.191</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.062</v>
       </c>
     </row>
     <row r="125">
@@ -6609,19 +6609,19 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.235</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.214</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.191</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.062</v>
       </c>
     </row>
     <row r="126">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17086,7 +17086,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -25524,7 +25524,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -38511,7 +38515,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -38594,7 +38598,7 @@
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
@@ -45092,7 +45096,7 @@
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
